--- a/output/pdf_financials_xlsx/BRW.xlsx
+++ b/output/pdf_financials_xlsx/BRW.xlsx
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.492705</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.489286</v>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5.492705</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.489286</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.245223</v>
+        <v>1.752518</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.818764</v>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -25326,7 +25326,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">

--- a/output/pdf_financials_xlsx/BRW.xlsx
+++ b/output/pdf_financials_xlsx/BRW.xlsx
@@ -1214,7 +1214,7 @@
         <v>-0.06418699999999999</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-5.551387</v>
+        <v>-5.412655</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-8.330880000000001</v>
+        <v>-8.018017</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.363595</v>
+        <v>0.443349</v>
       </c>
     </row>
     <row r="17">
@@ -1266,7 +1266,7 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.138732</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.312863</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.806944</v>
       </c>
     </row>
     <row r="18">
@@ -1824,7 +1824,7 @@
         <v>-0.06418699999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.551387</v>
+        <v>-5.412655</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-8.330880000000001</v>
+        <v>-8.018017</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.363595</v>
+        <v>0.443349</v>
       </c>
     </row>
     <row r="28">
@@ -1928,7 +1928,7 @@
         <v>-0.06418699999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.551387</v>
+        <v>-5.412655</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-8.330880000000001</v>
+        <v>-8.018017</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.363595</v>
+        <v>0.443349</v>
       </c>
     </row>
     <row r="30">
@@ -2042,7 +2042,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.563104428418216</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.901999708905581</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>407.5669506415939</v>
       </c>
     </row>
     <row r="32">
@@ -3978,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>0.9728869999999999</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.363863</v>
+        <v>0.312863</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>0</v>
@@ -4487,10 +4487,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J80" s="3" t="n">
+        <v>0.002292826801436928</v>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
@@ -6196,10 +6194,10 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.182025</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.731339</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -9217,7 +9215,11 @@
           <t>Current portion of lease obligation</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12884,7 +12886,11 @@
           <t>Issuance of Units pursuant to a private placement (Note 10)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -12953,7 +12959,11 @@
           <t>Issuance of flow-through shares pursuant to a non-brokered private placement (Note 10)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -13511,7 +13521,11 @@
           <t>Issuance of Units pursuant to a non-brokered private placement (Note 10)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -14148,7 +14162,11 @@
           <t>Issuance of Units pursuant to a private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -14219,7 +14237,11 @@
           <t>Issuance of Units pursuant to a non-brokered private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -14288,7 +14310,11 @@
           <t>Issuance of flow-through shares pursuant to a non-brokered private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -14359,7 +14385,11 @@
           <t>Issuance of Units and flow-through shares pursuant to a private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -15282,7 +15312,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -15353,7 +15387,11 @@
           <t>Issuance of Units and flow-through shares pursuant to a private placement (Note 13)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -15424,7 +15462,11 @@
           <t>Issuance of Units pursuant to a non-brokered private placement (Note 13)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -16838,7 +16880,11 @@
           <t>Proceeds from the sale of investments (Note 7)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -18849,7 +18895,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -19176,7 +19226,11 @@
           <t>Income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -24762,7 +24816,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
